--- a/sheets/민요/검수/새 타령-2.xlsx
+++ b/sheets/민요/검수/새 타령-2.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="2"/>
@@ -860,12 +860,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="2"/>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I46" s="2"/>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I55" s="2"/>
@@ -2817,12 +2817,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I61" s="2"/>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I66" s="2"/>
@@ -3157,12 +3157,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I70" s="2"/>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I75" s="2"/>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I76" s="3"/>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I78" s="2"/>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I87" s="2"/>
@@ -3839,12 +3839,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -4420,12 +4420,12 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I103" s="2"/>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I111" s="2"/>
@@ -4774,12 +4774,12 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4962,13 +4962,13 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G4" s="9"/>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="10"/>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="T5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U5" s="10"/>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="10"/>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K8" s="10"/>
@@ -5333,14 +5333,14 @@
       <c r="O8" s="10"/>
       <c r="P8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="Q8" s="10"/>
       <c r="R8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5451,7 +5451,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -5556,7 +5556,7 @@
       <c r="G11" s="10"/>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="10"/>
@@ -5589,7 +5589,7 @@
       <c r="S11" s="10"/>
       <c r="T11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U11" s="10"/>
@@ -5691,13 +5691,13 @@
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="9"/>
@@ -5770,20 +5770,20 @@
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -5806,21 +5806,21 @@
       <c r="M14" s="10"/>
       <c r="N14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="O14" s="10"/>
       <c r="P14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="Q14" s="10"/>
       <c r="R14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S14" s="10"/>
@@ -5942,7 +5942,7 @@
       <c r="S19" s="10"/>
       <c r="T19" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U19" s="10"/>
@@ -6185,7 +6185,7 @@
       <c r="S27" s="9"/>
       <c r="T27" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U27" s="9"/>
@@ -6212,7 +6212,7 @@
       <c r="S28" s="10"/>
       <c r="T28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/새 타령-2.xlsx
+++ b/sheets/민요/검수/새 타령-2.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4823,126 +4864,126 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">새 타령-2</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좌우</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="M3" s="22"/>
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
       </c>
-      <c r="R3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="R3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="T3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="T3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
@@ -4950,90 +4991,90 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="G4" s="23"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="23"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="R4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="S4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="T4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="T4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5041,161 +5082,161 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">꾀</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="I5" s="24"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="Q5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">으로</t>
         </is>
       </c>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">으로</t>
         </is>
       </c>
-      <c r="T5" s="17" t="inlineStr">
+      <c r="T5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U5" s="10"/>
+      <c r="U5" s="24"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꼬</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다아</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L6" s="17"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="L6" s="21"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="R6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="T6" s="17" t="inlineStr">
+      <c r="T6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="U6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우물</t>
         </is>
@@ -5203,154 +5244,154 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="23"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
-      <c r="L7" s="17"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="L7" s="21"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
       </c>
-      <c r="R7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="S7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
       </c>
-      <c r="T7" s="17" t="inlineStr">
+      <c r="T7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U7" s="9"/>
+      <c r="U7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">가아</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="G8" s="24"/>
+      <c r="H8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">녀</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="K8" s="24"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="Q8" s="24"/>
+      <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="S8" s="10"/>
-      <c r="T8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U8" s="10" t="inlineStr">
+      <c r="S8" s="24"/>
+      <c r="T8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5358,90 +5399,90 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南^</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울음</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울음</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울음</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L9" s="17"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="L9" s="21"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="S9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="U9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울음</t>
         </is>
@@ -5449,80 +5490,80 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="23"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="K10" s="23"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">삐</t>
         </is>
       </c>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="S10" s="9" t="inlineStr">
+      <c r="S10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
       </c>
-      <c r="T10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U10" s="9" t="inlineStr">
+      <c r="T10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -5530,152 +5571,152 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="24"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="24"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="24"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L11" s="17"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="L11" s="21"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
       </c>
-      <c r="R11" s="17"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="17" t="inlineStr">
+      <c r="R11" s="21"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U11" s="10"/>
+      <c r="U11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쁜</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L12" s="17"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="L12" s="21"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
+      <c r="S12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="T12" s="18" t="inlineStr">
+      <c r="T12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U12" s="11" t="inlineStr">
+      <c r="U12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5683,74 +5724,74 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="23"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
-      <c r="L13" s="17"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="L13" s="21"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="Q13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
       </c>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="S13" s="9" t="inlineStr">
+      <c r="S13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
       </c>
-      <c r="T13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U13" s="9" t="inlineStr">
+      <c r="T13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5758,132 +5799,132 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="24"/>
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="24"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="K14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="24"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="24"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="Q14" s="24"/>
+      <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="10"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="24"/>
     </row>
     <row r="15">
       <c r="A15" s="0"/>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">새 타령-2</t>
         </is>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="18" t="inlineStr">
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="U17" s="11" t="inlineStr">
+      <c r="U17" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">어디</t>
         </is>
@@ -5891,30 +5932,30 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U18" s="9" t="inlineStr">
+      <c r="B18" s="21"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -5922,58 +5963,58 @@
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="0"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="17" t="inlineStr">
+      <c r="B19" s="21"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U19" s="10"/>
+      <c r="U19" s="24"/>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="0"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="18" t="inlineStr">
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="U20" s="11" t="inlineStr">
+      <c r="U20" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5981,31 +6022,31 @@
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="0"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="17" t="inlineStr">
+      <c r="B21" s="21"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="21"/>
+      <c r="S21" s="23"/>
+      <c r="T21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U21" s="9" t="inlineStr">
+      <c r="U21" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -6013,58 +6054,58 @@
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="0"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U22" s="10"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U22" s="24"/>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="0"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="18" t="inlineStr">
+      <c r="B23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="21"/>
+      <c r="S23" s="22"/>
+      <c r="T23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U23" s="11" t="inlineStr">
+      <c r="U23" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -6072,30 +6113,30 @@
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="0"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U24" s="12" t="inlineStr">
+      <c r="B24" s="21"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U24" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">쁘</t>
         </is>
@@ -6103,30 +6144,30 @@
     </row>
     <row r="25" ht="56" customHeight="1">
       <c r="A25" s="0"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="17" t="inlineStr">
+      <c r="B25" s="21"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="21"/>
+      <c r="S25" s="24"/>
+      <c r="T25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U25" s="10" t="inlineStr">
+      <c r="U25" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -6134,30 +6175,30 @@
     </row>
     <row r="26" ht="56" customHeight="1">
       <c r="A26" s="0"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
+      <c r="B26" s="21"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="22"/>
+      <c r="T26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="U26" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -6165,58 +6206,58 @@
     </row>
     <row r="27" ht="56" customHeight="1">
       <c r="A27" s="0"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="17" t="inlineStr">
+      <c r="B27" s="21"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="23"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="23"/>
+      <c r="T27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U27" s="9"/>
+      <c r="U27" s="23"/>
     </row>
     <row r="28" ht="56" customHeight="1">
       <c r="A28" s="0"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="10"/>
-      <c r="T28" s="17" t="inlineStr">
+      <c r="B28" s="21"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="24"/>
+      <c r="R28" s="21"/>
+      <c r="S28" s="24"/>
+      <c r="T28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="U28" s="10"/>
+      <c r="U28" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/sheets/민요/검수/새 타령-2.xlsx
+++ b/sheets/민요/검수/새 타령-2.xlsx
@@ -4837,32 +4837,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="60.41" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="60.41" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="60.41" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="60.41" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="60.41" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="60.41" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="60.41" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="60.41" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="60.41" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="60.41" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="60.41" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="60.41" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="60.41" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
     <row r="15">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="60.41" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="60.41" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -5930,7 +5930,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="60.41" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="60.41" customHeight="1">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="U19" s="24"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="60.41" customHeight="1">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="60.41" customHeight="1">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="60.41" customHeight="1">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="60.41" customHeight="1">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="60.41" customHeight="1">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -6142,7 +6142,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="60.41" customHeight="1">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="60.41" customHeight="1">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -6204,7 +6204,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="60.41" customHeight="1">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="60.41" customHeight="1">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>

--- a/sheets/민요/검수/새 타령-2.xlsx
+++ b/sheets/민요/검수/새 타령-2.xlsx
@@ -4929,7 +4929,8 @@
       </c>
       <c r="I3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">좌우</t>
+          <t xml:space="preserve">좌
+우</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
@@ -5132,7 +5133,8 @@
       </c>
       <c r="Q5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">으로</t>
+          <t xml:space="preserve">으
+로</t>
         </is>
       </c>
       <c r="R5" s="21" t="inlineStr">
@@ -5143,7 +5145,8 @@
       </c>
       <c r="S5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">으로</t>
+          <t xml:space="preserve">으
+로</t>
         </is>
       </c>
       <c r="T5" s="21" t="inlineStr">
@@ -5193,7 +5196,8 @@
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">다아</t>
+          <t xml:space="preserve">다
+아</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -5238,7 +5242,8 @@
       </c>
       <c r="U6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우물</t>
+          <t xml:space="preserve">우
+물</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5348,8 @@
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">가아</t>
+          <t xml:space="preserve">가
+아</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -5417,7 +5423,8 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">울음</t>
+          <t xml:space="preserve">울
+음</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -5428,7 +5435,8 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">울음</t>
+          <t xml:space="preserve">울
+음</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -5439,7 +5447,8 @@
       </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">울음</t>
+          <t xml:space="preserve">울
+음</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -5484,7 +5493,8 @@
       </c>
       <c r="U9" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">울음</t>
+          <t xml:space="preserve">울
+음</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5936,8 @@
       </c>
       <c r="U17" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">어디</t>
+          <t xml:space="preserve">어
+디</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/새 타령-2.xlsx
+++ b/sheets/민요/검수/새 타령-2.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4896,7 +4919,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4906,7 +4929,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -4916,7 +4939,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
@@ -4927,7 +4950,7 @@
 南</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">좌
 우</t>
@@ -4938,7 +4961,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4948,13 +4971,13 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M3" s="22"/>
+      <c r="M3" s="29"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4964,7 +4987,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -4974,7 +4997,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S3" s="22" t="inlineStr">
+      <c r="S3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4984,7 +5007,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U3" s="22" t="inlineStr">
+      <c r="U3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
@@ -4997,7 +5020,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -5007,19 +5030,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="30"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -5029,7 +5052,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="K4" s="23" t="inlineStr">
+      <c r="K4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
@@ -5039,13 +5062,13 @@
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="M4" s="23"/>
+      <c r="M4" s="30"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="O4" s="23" t="inlineStr">
+      <c r="O4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5055,7 +5078,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q4" s="23" t="inlineStr">
+      <c r="Q4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -5065,7 +5088,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S4" s="23" t="inlineStr">
+      <c r="S4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -5075,7 +5098,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U4" s="23" t="inlineStr">
+      <c r="U4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5088,7 +5111,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -5098,7 +5121,7 @@
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">꾀</t>
         </is>
@@ -5108,7 +5131,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -5118,20 +5141,20 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="24"/>
+      <c r="I5" s="31"/>
       <c r="J5" s="21"/>
-      <c r="K5" s="24"/>
+      <c r="K5" s="31"/>
       <c r="L5" s="21"/>
-      <c r="M5" s="24"/>
+      <c r="M5" s="31"/>
       <c r="N5" s="21"/>
-      <c r="O5" s="24"/>
+      <c r="O5" s="31"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="Q5" s="24" t="inlineStr">
+      <c r="Q5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 로</t>
@@ -5143,7 +5166,7 @@
 南</t>
         </is>
       </c>
-      <c r="S5" s="24" t="inlineStr">
+      <c r="S5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 로</t>
@@ -5154,7 +5177,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U5" s="24"/>
+      <c r="U5" s="31"/>
     </row>
     <row r="6" ht="60.41" customHeight="1">
       <c r="A6" s="0"/>
@@ -5163,7 +5186,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5173,7 +5196,7 @@
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">꼬</t>
         </is>
@@ -5183,7 +5206,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
@@ -5194,7 +5217,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다
 아</t>
@@ -5205,21 +5228,21 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="L6" s="21"/>
-      <c r="M6" s="22"/>
+      <c r="M6" s="29"/>
       <c r="N6" s="21"/>
-      <c r="O6" s="22"/>
+      <c r="O6" s="29"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5229,7 +5252,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S6" s="22" t="inlineStr">
+      <c r="S6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5240,7 +5263,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="U6" s="22" t="inlineStr">
+      <c r="U6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 물</t>
@@ -5254,7 +5277,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5264,7 +5287,7 @@
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -5274,7 +5297,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -5285,27 +5308,27 @@
 無</t>
         </is>
       </c>
-      <c r="I7" s="23"/>
+      <c r="I7" s="30"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
       <c r="L7" s="21"/>
-      <c r="M7" s="23"/>
+      <c r="M7" s="30"/>
       <c r="N7" s="21"/>
-      <c r="O7" s="23"/>
+      <c r="O7" s="30"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q7" s="23" t="inlineStr">
+      <c r="Q7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
@@ -5315,7 +5338,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S7" s="23" t="inlineStr">
+      <c r="S7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
@@ -5326,7 +5349,7 @@
 無</t>
         </is>
       </c>
-      <c r="U7" s="23"/>
+      <c r="U7" s="30"/>
     </row>
     <row r="8" ht="60.41" customHeight="1">
       <c r="A8" s="0"/>
@@ -5335,7 +5358,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5346,7 +5369,7 @@
 無</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 아</t>
@@ -5357,13 +5380,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="24"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">녀</t>
         </is>
@@ -5373,31 +5396,31 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K8" s="24"/>
+      <c r="K8" s="31"/>
       <c r="L8" s="21"/>
-      <c r="M8" s="24"/>
+      <c r="M8" s="31"/>
       <c r="N8" s="21"/>
-      <c r="O8" s="24"/>
+      <c r="O8" s="31"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q8" s="24"/>
+      <c r="Q8" s="31"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="S8" s="24"/>
+      <c r="S8" s="31"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U8" s="24" t="inlineStr">
+      <c r="U8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5410,7 +5433,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5421,7 +5444,7 @@
 南^</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">울
 음</t>
@@ -5433,7 +5456,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">울
 음</t>
@@ -5445,7 +5468,7 @@
 無</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">울
 음</t>
@@ -5456,21 +5479,21 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="L9" s="21"/>
-      <c r="M9" s="22"/>
+      <c r="M9" s="29"/>
       <c r="N9" s="21"/>
-      <c r="O9" s="22"/>
+      <c r="O9" s="29"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -5480,7 +5503,7 @@
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="S9" s="22" t="inlineStr">
+      <c r="S9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -5491,7 +5514,7 @@
 無</t>
         </is>
       </c>
-      <c r="U9" s="22" t="inlineStr">
+      <c r="U9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">울
 음</t>
@@ -5506,13 +5529,13 @@
 㴌</t>
         </is>
       </c>
-      <c r="C10" s="23"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -5522,7 +5545,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -5532,7 +5555,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -5543,17 +5566,17 @@
 㴌</t>
         </is>
       </c>
-      <c r="K10" s="23"/>
+      <c r="K10" s="30"/>
       <c r="L10" s="21"/>
-      <c r="M10" s="23"/>
+      <c r="M10" s="30"/>
       <c r="N10" s="21"/>
-      <c r="O10" s="23"/>
+      <c r="O10" s="30"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="Q10" s="23" t="inlineStr">
+      <c r="Q10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">삐</t>
         </is>
@@ -5563,7 +5586,7 @@
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="S10" s="23" t="inlineStr">
+      <c r="S10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
@@ -5573,7 +5596,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U10" s="23" t="inlineStr">
+      <c r="U10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -5587,7 +5610,7 @@
 無</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -5597,53 +5620,53 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E11" s="24"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G11" s="24"/>
+      <c r="G11" s="31"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="24"/>
+      <c r="I11" s="31"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K11" s="24" t="inlineStr">
+      <c r="K11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="L11" s="21"/>
-      <c r="M11" s="24"/>
+      <c r="M11" s="31"/>
       <c r="N11" s="21"/>
-      <c r="O11" s="24"/>
+      <c r="O11" s="31"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="Q11" s="24" t="inlineStr">
+      <c r="Q11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
       </c>
       <c r="R11" s="21"/>
-      <c r="S11" s="24"/>
+      <c r="S11" s="31"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U11" s="24"/>
+      <c r="U11" s="31"/>
     </row>
     <row r="12" ht="60.41" customHeight="1">
       <c r="A12" s="0"/>
@@ -5652,7 +5675,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">쁜</t>
         </is>
@@ -5662,7 +5685,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5672,7 +5695,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5682,7 +5705,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5692,21 +5715,21 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="L12" s="21"/>
-      <c r="M12" s="22"/>
+      <c r="M12" s="29"/>
       <c r="N12" s="21"/>
-      <c r="O12" s="22"/>
+      <c r="O12" s="29"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -5716,7 +5739,7 @@
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="S12" s="22" t="inlineStr">
+      <c r="S12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -5726,7 +5749,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U12" s="27" t="inlineStr">
+      <c r="U12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5739,25 +5762,25 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C13" s="23"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="23"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5767,21 +5790,21 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K13" s="23" t="inlineStr">
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
       <c r="L13" s="21"/>
-      <c r="M13" s="23"/>
+      <c r="M13" s="30"/>
       <c r="N13" s="21"/>
-      <c r="O13" s="23"/>
+      <c r="O13" s="30"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="Q13" s="23" t="inlineStr">
+      <c r="Q13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
@@ -5791,7 +5814,7 @@
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="S13" s="23" t="inlineStr">
+      <c r="S13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
@@ -5801,7 +5824,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U13" s="23" t="inlineStr">
+      <c r="U13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5814,7 +5837,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -5825,26 +5848,26 @@
 △</t>
         </is>
       </c>
-      <c r="E14" s="24"/>
+      <c r="E14" s="31"/>
       <c r="F14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I14" s="24"/>
+      <c r="I14" s="31"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K14" s="24" t="inlineStr">
+      <c r="K14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5854,29 +5877,29 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M14" s="24"/>
+      <c r="M14" s="31"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O14" s="24"/>
+      <c r="O14" s="31"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q14" s="24"/>
+      <c r="Q14" s="31"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S14" s="24"/>
+      <c r="S14" s="31"/>
       <c r="T14" s="21"/>
-      <c r="U14" s="24"/>
+      <c r="U14" s="31"/>
     </row>
     <row r="15">
       <c r="A15" s="0"/>
@@ -5911,30 +5934,30 @@
     <row r="17" ht="60.41" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
-      <c r="C17" s="22"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="21"/>
-      <c r="E17" s="22"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="21"/>
-      <c r="G17" s="22"/>
+      <c r="G17" s="29"/>
       <c r="H17" s="21"/>
-      <c r="I17" s="22"/>
+      <c r="I17" s="29"/>
       <c r="J17" s="21"/>
-      <c r="K17" s="22"/>
+      <c r="K17" s="29"/>
       <c r="L17" s="21"/>
-      <c r="M17" s="22"/>
+      <c r="M17" s="29"/>
       <c r="N17" s="21"/>
-      <c r="O17" s="22"/>
+      <c r="O17" s="29"/>
       <c r="P17" s="21"/>
-      <c r="Q17" s="22"/>
+      <c r="Q17" s="29"/>
       <c r="R17" s="21"/>
-      <c r="S17" s="22"/>
+      <c r="S17" s="29"/>
       <c r="T17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="U17" s="27" t="inlineStr">
+      <c r="U17" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 디</t>
@@ -5944,29 +5967,29 @@
     <row r="18" ht="60.41" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
-      <c r="C18" s="23"/>
+      <c r="C18" s="30"/>
       <c r="D18" s="21"/>
-      <c r="E18" s="23"/>
+      <c r="E18" s="30"/>
       <c r="F18" s="21"/>
-      <c r="G18" s="23"/>
+      <c r="G18" s="30"/>
       <c r="H18" s="21"/>
-      <c r="I18" s="23"/>
+      <c r="I18" s="30"/>
       <c r="J18" s="21"/>
-      <c r="K18" s="23"/>
+      <c r="K18" s="30"/>
       <c r="L18" s="21"/>
-      <c r="M18" s="23"/>
+      <c r="M18" s="30"/>
       <c r="N18" s="21"/>
-      <c r="O18" s="23"/>
+      <c r="O18" s="30"/>
       <c r="P18" s="21"/>
-      <c r="Q18" s="23"/>
+      <c r="Q18" s="30"/>
       <c r="R18" s="21"/>
-      <c r="S18" s="23"/>
+      <c r="S18" s="30"/>
       <c r="T18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U18" s="23" t="inlineStr">
+      <c r="U18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -5975,57 +5998,57 @@
     <row r="19" ht="60.41" customHeight="1">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
-      <c r="C19" s="24"/>
+      <c r="C19" s="31"/>
       <c r="D19" s="21"/>
-      <c r="E19" s="24"/>
+      <c r="E19" s="31"/>
       <c r="F19" s="21"/>
-      <c r="G19" s="24"/>
+      <c r="G19" s="31"/>
       <c r="H19" s="21"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="31"/>
       <c r="J19" s="21"/>
-      <c r="K19" s="24"/>
+      <c r="K19" s="31"/>
       <c r="L19" s="21"/>
-      <c r="M19" s="24"/>
+      <c r="M19" s="31"/>
       <c r="N19" s="21"/>
-      <c r="O19" s="24"/>
+      <c r="O19" s="31"/>
       <c r="P19" s="21"/>
-      <c r="Q19" s="24"/>
+      <c r="Q19" s="31"/>
       <c r="R19" s="21"/>
-      <c r="S19" s="24"/>
+      <c r="S19" s="31"/>
       <c r="T19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U19" s="24"/>
+      <c r="U19" s="31"/>
     </row>
     <row r="20" ht="60.41" customHeight="1">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
-      <c r="C20" s="22"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="21"/>
-      <c r="E20" s="22"/>
+      <c r="E20" s="29"/>
       <c r="F20" s="21"/>
-      <c r="G20" s="22"/>
+      <c r="G20" s="29"/>
       <c r="H20" s="21"/>
-      <c r="I20" s="22"/>
+      <c r="I20" s="29"/>
       <c r="J20" s="21"/>
-      <c r="K20" s="22"/>
+      <c r="K20" s="29"/>
       <c r="L20" s="21"/>
-      <c r="M20" s="22"/>
+      <c r="M20" s="29"/>
       <c r="N20" s="21"/>
-      <c r="O20" s="22"/>
+      <c r="O20" s="29"/>
       <c r="P20" s="21"/>
-      <c r="Q20" s="22"/>
+      <c r="Q20" s="29"/>
       <c r="R20" s="21"/>
-      <c r="S20" s="22"/>
+      <c r="S20" s="29"/>
       <c r="T20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="U20" s="27" t="inlineStr">
+      <c r="U20" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -6034,30 +6057,30 @@
     <row r="21" ht="60.41" customHeight="1">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
-      <c r="C21" s="23"/>
+      <c r="C21" s="30"/>
       <c r="D21" s="21"/>
-      <c r="E21" s="23"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="21"/>
-      <c r="G21" s="23"/>
+      <c r="G21" s="30"/>
       <c r="H21" s="21"/>
-      <c r="I21" s="23"/>
+      <c r="I21" s="30"/>
       <c r="J21" s="21"/>
-      <c r="K21" s="23"/>
+      <c r="K21" s="30"/>
       <c r="L21" s="21"/>
-      <c r="M21" s="23"/>
+      <c r="M21" s="30"/>
       <c r="N21" s="21"/>
-      <c r="O21" s="23"/>
+      <c r="O21" s="30"/>
       <c r="P21" s="21"/>
-      <c r="Q21" s="23"/>
+      <c r="Q21" s="30"/>
       <c r="R21" s="21"/>
-      <c r="S21" s="23"/>
+      <c r="S21" s="30"/>
       <c r="T21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U21" s="23" t="inlineStr">
+      <c r="U21" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -6066,57 +6089,57 @@
     <row r="22" ht="60.41" customHeight="1">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
-      <c r="C22" s="24"/>
+      <c r="C22" s="31"/>
       <c r="D22" s="21"/>
-      <c r="E22" s="24"/>
+      <c r="E22" s="31"/>
       <c r="F22" s="21"/>
-      <c r="G22" s="24"/>
+      <c r="G22" s="31"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="24"/>
+      <c r="I22" s="31"/>
       <c r="J22" s="21"/>
-      <c r="K22" s="24"/>
+      <c r="K22" s="31"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="24"/>
+      <c r="M22" s="31"/>
       <c r="N22" s="21"/>
-      <c r="O22" s="24"/>
+      <c r="O22" s="31"/>
       <c r="P22" s="21"/>
-      <c r="Q22" s="24"/>
+      <c r="Q22" s="31"/>
       <c r="R22" s="21"/>
-      <c r="S22" s="24"/>
+      <c r="S22" s="31"/>
       <c r="T22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U22" s="24"/>
+      <c r="U22" s="31"/>
     </row>
     <row r="23" ht="60.41" customHeight="1">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
-      <c r="C23" s="22"/>
+      <c r="C23" s="29"/>
       <c r="D23" s="21"/>
-      <c r="E23" s="22"/>
+      <c r="E23" s="29"/>
       <c r="F23" s="21"/>
-      <c r="G23" s="22"/>
+      <c r="G23" s="29"/>
       <c r="H23" s="21"/>
-      <c r="I23" s="22"/>
+      <c r="I23" s="29"/>
       <c r="J23" s="21"/>
-      <c r="K23" s="22"/>
+      <c r="K23" s="29"/>
       <c r="L23" s="21"/>
-      <c r="M23" s="22"/>
+      <c r="M23" s="29"/>
       <c r="N23" s="21"/>
-      <c r="O23" s="22"/>
+      <c r="O23" s="29"/>
       <c r="P23" s="21"/>
-      <c r="Q23" s="22"/>
+      <c r="Q23" s="29"/>
       <c r="R23" s="21"/>
-      <c r="S23" s="22"/>
+      <c r="S23" s="29"/>
       <c r="T23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U23" s="27" t="inlineStr">
+      <c r="U23" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -6125,29 +6148,29 @@
     <row r="24" ht="60.41" customHeight="1">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
-      <c r="C24" s="23"/>
+      <c r="C24" s="30"/>
       <c r="D24" s="21"/>
-      <c r="E24" s="23"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="21"/>
-      <c r="G24" s="23"/>
+      <c r="G24" s="30"/>
       <c r="H24" s="21"/>
-      <c r="I24" s="23"/>
+      <c r="I24" s="30"/>
       <c r="J24" s="21"/>
-      <c r="K24" s="23"/>
+      <c r="K24" s="30"/>
       <c r="L24" s="21"/>
-      <c r="M24" s="23"/>
+      <c r="M24" s="30"/>
       <c r="N24" s="21"/>
-      <c r="O24" s="23"/>
+      <c r="O24" s="30"/>
       <c r="P24" s="21"/>
-      <c r="Q24" s="23"/>
+      <c r="Q24" s="30"/>
       <c r="R24" s="21"/>
-      <c r="S24" s="23"/>
+      <c r="S24" s="30"/>
       <c r="T24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U24" s="28" t="inlineStr">
+      <c r="U24" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">쁘</t>
         </is>
@@ -6156,29 +6179,29 @@
     <row r="25" ht="60.41" customHeight="1">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
-      <c r="C25" s="24"/>
+      <c r="C25" s="31"/>
       <c r="D25" s="21"/>
-      <c r="E25" s="24"/>
+      <c r="E25" s="31"/>
       <c r="F25" s="21"/>
-      <c r="G25" s="24"/>
+      <c r="G25" s="31"/>
       <c r="H25" s="21"/>
-      <c r="I25" s="24"/>
+      <c r="I25" s="31"/>
       <c r="J25" s="21"/>
-      <c r="K25" s="24"/>
+      <c r="K25" s="31"/>
       <c r="L25" s="21"/>
-      <c r="M25" s="24"/>
+      <c r="M25" s="31"/>
       <c r="N25" s="21"/>
-      <c r="O25" s="24"/>
+      <c r="O25" s="31"/>
       <c r="P25" s="21"/>
-      <c r="Q25" s="24"/>
+      <c r="Q25" s="31"/>
       <c r="R25" s="21"/>
-      <c r="S25" s="24"/>
+      <c r="S25" s="31"/>
       <c r="T25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U25" s="24" t="inlineStr">
+      <c r="U25" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -6187,29 +6210,29 @@
     <row r="26" ht="60.41" customHeight="1">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
-      <c r="C26" s="22"/>
+      <c r="C26" s="29"/>
       <c r="D26" s="21"/>
-      <c r="E26" s="22"/>
+      <c r="E26" s="29"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="22"/>
+      <c r="G26" s="29"/>
       <c r="H26" s="21"/>
-      <c r="I26" s="22"/>
+      <c r="I26" s="29"/>
       <c r="J26" s="21"/>
-      <c r="K26" s="22"/>
+      <c r="K26" s="29"/>
       <c r="L26" s="21"/>
-      <c r="M26" s="22"/>
+      <c r="M26" s="29"/>
       <c r="N26" s="21"/>
-      <c r="O26" s="22"/>
+      <c r="O26" s="29"/>
       <c r="P26" s="21"/>
-      <c r="Q26" s="22"/>
+      <c r="Q26" s="29"/>
       <c r="R26" s="21"/>
-      <c r="S26" s="22"/>
+      <c r="S26" s="29"/>
       <c r="T26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U26" s="22" t="inlineStr">
+      <c r="U26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -6218,57 +6241,57 @@
     <row r="27" ht="60.41" customHeight="1">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
-      <c r="C27" s="23"/>
+      <c r="C27" s="30"/>
       <c r="D27" s="21"/>
-      <c r="E27" s="23"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="21"/>
-      <c r="G27" s="23"/>
+      <c r="G27" s="30"/>
       <c r="H27" s="21"/>
-      <c r="I27" s="23"/>
+      <c r="I27" s="30"/>
       <c r="J27" s="21"/>
-      <c r="K27" s="23"/>
+      <c r="K27" s="30"/>
       <c r="L27" s="21"/>
-      <c r="M27" s="23"/>
+      <c r="M27" s="30"/>
       <c r="N27" s="21"/>
-      <c r="O27" s="23"/>
+      <c r="O27" s="30"/>
       <c r="P27" s="21"/>
-      <c r="Q27" s="23"/>
+      <c r="Q27" s="30"/>
       <c r="R27" s="21"/>
-      <c r="S27" s="23"/>
+      <c r="S27" s="30"/>
       <c r="T27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U27" s="23"/>
+      <c r="U27" s="30"/>
     </row>
     <row r="28" ht="60.41" customHeight="1">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
-      <c r="C28" s="24"/>
+      <c r="C28" s="31"/>
       <c r="D28" s="21"/>
-      <c r="E28" s="24"/>
+      <c r="E28" s="31"/>
       <c r="F28" s="21"/>
-      <c r="G28" s="24"/>
+      <c r="G28" s="31"/>
       <c r="H28" s="21"/>
-      <c r="I28" s="24"/>
+      <c r="I28" s="31"/>
       <c r="J28" s="21"/>
-      <c r="K28" s="24"/>
+      <c r="K28" s="31"/>
       <c r="L28" s="21"/>
-      <c r="M28" s="24"/>
+      <c r="M28" s="31"/>
       <c r="N28" s="21"/>
-      <c r="O28" s="24"/>
+      <c r="O28" s="31"/>
       <c r="P28" s="21"/>
-      <c r="Q28" s="24"/>
+      <c r="Q28" s="31"/>
       <c r="R28" s="21"/>
-      <c r="S28" s="24"/>
+      <c r="S28" s="31"/>
       <c r="T28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="U28" s="24"/>
+      <c r="U28" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/sheets/민요/검수/새 타령-2.xlsx
+++ b/sheets/민요/검수/새 타령-2.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -241,24 +236,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -369,7 +346,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
@@ -429,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손으로 그린 12정간 격자(굵은 가로선 3칸마다 → 3/4). 상단 여백에 "새타령 (2절)", "C# 키 ⟷ C키" 메모. 격자 안 율명 줄은 10줄이고, 11줄은 왼쪽 테두리 밖 여백에 율명을 적고 테두리 안쪽 좁은 칸에 가사를 적음. 12·13줄은 원본에 없어 빈 정간으로 둠(#줄수 13은 기존 구조 유지, 실제 11줄). 4줄 3~11정간은 세로 연음선, 5줄 10~11정간은 세로 물결선만 있어 비움. 潢|無 칸의 요성 물결선, 潕 옆 C형·&lt; 꾸밈은 생략. 2026-10 재검수: 줄 배치 전면 재판독.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 12정간 격자(굵은 가로선 3칸마다) → 3/4·12. 상단 "&lt;2절&gt; 새타령(2) C#키⟷C키". 오른쪽부터 11줄(11줄은 왼쪽 테두리 밖 여백에 율명, 테두리 안 좁은 칸에 가사). 한 곡. 4줄 3~11정간 세로 연음선, 5줄 10~11정간 세로 물결선만 있어 비움. 潢|無 칸의 요성 물결선 생략. 潕 옆 C·&lt; 모양 꾸밈과 㴌·南 옆 ^ 꾸밈은 ^ 로 적음. 4줄 2정간 淋 아래 작은 물결 표시 생략.</t>
         </is>
       </c>
     </row>
@@ -974,7 +951,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">획 겹쳐 흘림, 7줄 10정간과 같은 가락으로 姑</t>
+          <t xml:space="preserve">획을 덧써 지운 듯 흘림. 7줄 10정간과 같은 가락으로 姑</t>
         </is>
       </c>
       <c r="K11" s="2"/>
@@ -1273,17 +1250,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕^</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕^</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">삐</t>
         </is>
       </c>
       <c r="J19" s="4"/>
@@ -1351,17 +1328,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕^</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕^</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">삐</t>
         </is>
       </c>
       <c r="J21" s="4"/>
@@ -1696,17 +1673,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕^</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕^</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">삐</t>
         </is>
       </c>
       <c r="J30" s="4"/>
@@ -1735,12 +1712,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕^</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
+          <t xml:space="preserve">潕^</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1823,7 +1800,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">삐</t>
         </is>
       </c>
       <c r="J33" s="4"/>
@@ -3443,22 +3420,22 @@
       <c r="F76" s="2">
         <v>4</v>
       </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I76" s="3"/>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아주 작은 점, ·일 수도</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아주 작은 표시. –일 수도</t>
+        </is>
+      </c>
+      <c r="J76" s="4"/>
       <c r="K76" s="2"/>
     </row>
     <row r="77">
@@ -4399,27 +4376,23 @@
       <c r="F101" s="2">
         <v>1</v>
       </c>
-      <c r="G101" s="3" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南|南</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="I101" s="3" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">어디</t>
         </is>
       </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">테두리 밖 여백</t>
-        </is>
-      </c>
+      <c r="J101" s="4"/>
       <c r="K101" s="2"/>
     </row>
     <row r="102">
@@ -4517,27 +4490,23 @@
       <c r="F104" s="2">
         <v>2</v>
       </c>
-      <c r="G104" s="3" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|㴌</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="I104" s="3" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">윗글자 氵 부분이 종이 끝에 걸림, 7줄 4정간과 같은 가락으로 潢</t>
-        </is>
-      </c>
+      <c r="J104" s="4"/>
       <c r="K104" s="2"/>
     </row>
     <row r="105">
@@ -4636,27 +4605,23 @@
       <c r="F107" s="2">
         <v>3</v>
       </c>
-      <c r="G107" s="3" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|無</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I107" s="3" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 기?</t>
-        </is>
-      </c>
+      <c r="J107" s="4"/>
       <c r="K107" s="2"/>
     </row>
     <row r="108">
@@ -4697,7 +4662,7 @@
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 버/쁘?</t>
+          <t xml:space="preserve">가사 쁘/버?</t>
         </is>
       </c>
       <c r="K108" s="2"/>
@@ -4885,7 +4850,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.41" customHeight="1">
+    <row r="2" ht="143.26" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4912,14 +4877,14 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="60.41" customHeight="1">
+    <row r="3" ht="143.26" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4929,7 +4894,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -4939,7 +4904,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
@@ -4950,7 +4915,7 @@
 南</t>
         </is>
       </c>
-      <c r="I3" s="29" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좌
 우</t>
@@ -4961,7 +4926,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4971,13 +4936,13 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M3" s="29"/>
+      <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O3" s="29" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4987,7 +4952,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q3" s="29" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">저</t>
         </is>
@@ -4997,7 +4962,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S3" s="29" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -5007,20 +4972,20 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U3" s="29" t="inlineStr">
+      <c r="U3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60.41" customHeight="1">
+    <row r="4" ht="143.26" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -5030,19 +4995,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="30"/>
+      <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="30"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="30" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -5052,7 +5017,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="K4" s="30" t="inlineStr">
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
@@ -5062,13 +5027,13 @@
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="M4" s="30"/>
+      <c r="M4" s="23"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="O4" s="30" t="inlineStr">
+      <c r="O4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -5078,7 +5043,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q4" s="30" t="inlineStr">
+      <c r="Q4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -5088,7 +5053,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S4" s="30" t="inlineStr">
+      <c r="S4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -5098,20 +5063,20 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U4" s="30" t="inlineStr">
+      <c r="U4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60.41" customHeight="1">
+    <row r="5" ht="143.26" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -5121,7 +5086,7 @@
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">꾀</t>
         </is>
@@ -5131,7 +5096,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G5" s="31" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -5141,20 +5106,20 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="31"/>
+      <c r="I5" s="24"/>
       <c r="J5" s="21"/>
-      <c r="K5" s="31"/>
+      <c r="K5" s="24"/>
       <c r="L5" s="21"/>
-      <c r="M5" s="31"/>
+      <c r="M5" s="24"/>
       <c r="N5" s="21"/>
-      <c r="O5" s="31"/>
+      <c r="O5" s="24"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="Q5" s="31" t="inlineStr">
+      <c r="Q5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 로</t>
@@ -5166,7 +5131,7 @@
 南</t>
         </is>
       </c>
-      <c r="S5" s="31" t="inlineStr">
+      <c r="S5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">으
 로</t>
@@ -5177,16 +5142,16 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U5" s="31"/>
-    </row>
-    <row r="6" ht="60.41" customHeight="1">
+      <c r="U5" s="24"/>
+    </row>
+    <row r="6" ht="143.26" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5196,7 +5161,7 @@
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꼬</t>
         </is>
@@ -5206,7 +5171,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
@@ -5217,7 +5182,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다
 아</t>
@@ -5228,21 +5193,21 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="29" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="L6" s="21"/>
-      <c r="M6" s="29"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="21"/>
-      <c r="O6" s="29"/>
+      <c r="O6" s="22"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q6" s="29" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5252,7 +5217,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S6" s="29" t="inlineStr">
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -5263,21 +5228,21 @@
 㴌</t>
         </is>
       </c>
-      <c r="U6" s="29" t="inlineStr">
+      <c r="U6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 물</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60.41" customHeight="1">
+    <row r="7" ht="143.26" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5287,7 +5252,7 @@
           <t xml:space="preserve">㴌^</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -5297,7 +5262,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G7" s="30" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -5308,27 +5273,27 @@
 無</t>
         </is>
       </c>
-      <c r="I7" s="30"/>
+      <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="30" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
       <c r="L7" s="21"/>
-      <c r="M7" s="30"/>
+      <c r="M7" s="23"/>
       <c r="N7" s="21"/>
-      <c r="O7" s="30"/>
+      <c r="O7" s="23"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q7" s="30" t="inlineStr">
+      <c r="Q7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
@@ -5338,7 +5303,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S7" s="30" t="inlineStr">
+      <c r="S7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
@@ -5349,16 +5314,16 @@
 無</t>
         </is>
       </c>
-      <c r="U7" s="30"/>
-    </row>
-    <row r="8" ht="60.41" customHeight="1">
+      <c r="U7" s="23"/>
+    </row>
+    <row r="8" ht="143.26" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -5369,7 +5334,7 @@
 無</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 아</t>
@@ -5380,13 +5345,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="31"/>
+      <c r="G8" s="24"/>
       <c r="H8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I8" s="32" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">녀</t>
         </is>
@@ -5396,44 +5361,44 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K8" s="31"/>
+      <c r="K8" s="24"/>
       <c r="L8" s="21"/>
-      <c r="M8" s="31"/>
+      <c r="M8" s="24"/>
       <c r="N8" s="21"/>
-      <c r="O8" s="31"/>
+      <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q8" s="31"/>
+      <c r="Q8" s="24"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="S8" s="31"/>
+      <c r="S8" s="24"/>
       <c r="T8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U8" s="31" t="inlineStr">
+      <c r="U8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60.41" customHeight="1">
+    <row r="9" ht="143.26" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -5444,7 +5409,7 @@
 南^</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울
 음</t>
@@ -5456,7 +5421,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울
 음</t>
@@ -5468,7 +5433,7 @@
 無</t>
         </is>
       </c>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울
 음</t>
@@ -5479,33 +5444,33 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="29" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="L9" s="21"/>
-      <c r="M9" s="29"/>
+      <c r="M9" s="22"/>
       <c r="N9" s="21"/>
-      <c r="O9" s="29"/>
+      <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="Q9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">潕^</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삐</t>
         </is>
       </c>
       <c r="R9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="S9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">潕^</t>
+        </is>
+      </c>
+      <c r="S9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삐</t>
         </is>
       </c>
       <c r="T9" s="21" t="inlineStr">
@@ -5514,14 +5479,14 @@
 無</t>
         </is>
       </c>
-      <c r="U9" s="29" t="inlineStr">
+      <c r="U9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">울
 음</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60.41" customHeight="1">
+    <row r="10" ht="143.26" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5529,13 +5494,13 @@
 㴌</t>
         </is>
       </c>
-      <c r="C10" s="30"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南^</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -5545,7 +5510,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G10" s="30" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -5555,7 +5520,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I10" s="30" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -5566,17 +5531,17 @@
 㴌</t>
         </is>
       </c>
-      <c r="K10" s="30"/>
+      <c r="K10" s="23"/>
       <c r="L10" s="21"/>
-      <c r="M10" s="30"/>
+      <c r="M10" s="23"/>
       <c r="N10" s="21"/>
-      <c r="O10" s="30"/>
+      <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="Q10" s="30" t="inlineStr">
+          <t xml:space="preserve">潕^</t>
+        </is>
+      </c>
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">삐</t>
         </is>
@@ -5586,7 +5551,7 @@
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="S10" s="30" t="inlineStr">
+      <c r="S10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
@@ -5596,13 +5561,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U10" s="30" t="inlineStr">
+      <c r="U10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60.41" customHeight="1">
+    <row r="11" ht="143.26" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5610,7 +5575,7 @@
 無</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
@@ -5620,62 +5585,62 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E11" s="31"/>
+      <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G11" s="31"/>
+      <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="31"/>
+      <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K11" s="31" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="L11" s="21"/>
-      <c r="M11" s="31"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="21"/>
-      <c r="O11" s="31"/>
+      <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="Q11" s="31" t="inlineStr">
+      <c r="Q11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
       </c>
       <c r="R11" s="21"/>
-      <c r="S11" s="31"/>
+      <c r="S11" s="24"/>
       <c r="T11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U11" s="31"/>
-    </row>
-    <row r="12" ht="60.41" customHeight="1">
+      <c r="U11" s="24"/>
+    </row>
+    <row r="12" ht="143.26" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쁜</t>
         </is>
@@ -5685,7 +5650,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5695,7 +5660,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="G12" s="29" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5705,7 +5670,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="29" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -5715,33 +5680,33 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K12" s="29" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
       <c r="L12" s="21"/>
-      <c r="M12" s="29"/>
+      <c r="M12" s="22"/>
       <c r="N12" s="21"/>
-      <c r="O12" s="29"/>
+      <c r="O12" s="22"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="Q12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삐</t>
         </is>
       </c>
       <c r="R12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="S12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">潕^</t>
+        </is>
+      </c>
+      <c r="S12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삐</t>
         </is>
       </c>
       <c r="T12" s="25" t="inlineStr">
@@ -5749,38 +5714,38 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U12" s="33" t="inlineStr">
+      <c r="U12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60.41" customHeight="1">
+    <row r="13" ht="143.26" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C13" s="30"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="30"/>
+      <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="30"/>
+      <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I13" s="30" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5790,21 +5755,21 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K13" s="30" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
       <c r="L13" s="21"/>
-      <c r="M13" s="30"/>
+      <c r="M13" s="23"/>
       <c r="N13" s="21"/>
-      <c r="O13" s="30"/>
+      <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="Q13" s="30" t="inlineStr">
+      <c r="Q13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
@@ -5814,7 +5779,7 @@
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="S13" s="30" t="inlineStr">
+      <c r="S13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">꾹</t>
         </is>
@@ -5824,20 +5789,20 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U13" s="30" t="inlineStr">
+      <c r="U13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60.41" customHeight="1">
+    <row r="14" ht="143.26" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -5848,26 +5813,40 @@
 △</t>
         </is>
       </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="E14" s="24"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="32"/>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+주
+작
+은
+표
+시
+.
+–
+일
+수
+도</t>
+        </is>
+      </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I14" s="31"/>
+      <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K14" s="31" t="inlineStr">
+      <c r="K14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -5877,34 +5856,34 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M14" s="31"/>
+      <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O14" s="31"/>
+      <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q14" s="31"/>
+      <c r="Q14" s="24"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S14" s="31"/>
+      <c r="S14" s="24"/>
       <c r="T14" s="21"/>
-      <c r="U14" s="31"/>
+      <c r="U14" s="24"/>
     </row>
     <row r="15">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60.41" customHeight="1">
+    <row r="16" ht="143.26" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -5931,367 +5910,367 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="60.41" customHeight="1">
+    <row r="17" ht="143.26" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
-      <c r="C17" s="29"/>
+      <c r="C17" s="22"/>
       <c r="D17" s="21"/>
-      <c r="E17" s="29"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="21"/>
-      <c r="G17" s="29"/>
+      <c r="G17" s="22"/>
       <c r="H17" s="21"/>
-      <c r="I17" s="29"/>
+      <c r="I17" s="22"/>
       <c r="J17" s="21"/>
-      <c r="K17" s="29"/>
+      <c r="K17" s="22"/>
       <c r="L17" s="21"/>
-      <c r="M17" s="29"/>
+      <c r="M17" s="22"/>
       <c r="N17" s="21"/>
-      <c r="O17" s="29"/>
+      <c r="O17" s="22"/>
       <c r="P17" s="21"/>
-      <c r="Q17" s="29"/>
+      <c r="Q17" s="22"/>
       <c r="R17" s="21"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="25" t="inlineStr">
+      <c r="S17" s="22"/>
+      <c r="T17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="U17" s="33" t="inlineStr">
+      <c r="U17" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 디</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60.41" customHeight="1">
+    <row r="18" ht="143.26" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
-      <c r="C18" s="30"/>
+      <c r="C18" s="23"/>
       <c r="D18" s="21"/>
-      <c r="E18" s="30"/>
+      <c r="E18" s="23"/>
       <c r="F18" s="21"/>
-      <c r="G18" s="30"/>
+      <c r="G18" s="23"/>
       <c r="H18" s="21"/>
-      <c r="I18" s="30"/>
+      <c r="I18" s="23"/>
       <c r="J18" s="21"/>
-      <c r="K18" s="30"/>
+      <c r="K18" s="23"/>
       <c r="L18" s="21"/>
-      <c r="M18" s="30"/>
+      <c r="M18" s="23"/>
       <c r="N18" s="21"/>
-      <c r="O18" s="30"/>
+      <c r="O18" s="23"/>
       <c r="P18" s="21"/>
-      <c r="Q18" s="30"/>
+      <c r="Q18" s="23"/>
       <c r="R18" s="21"/>
-      <c r="S18" s="30"/>
+      <c r="S18" s="23"/>
       <c r="T18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U18" s="30" t="inlineStr">
+      <c r="U18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60.41" customHeight="1">
+    <row r="19" ht="143.26" customHeight="1">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
-      <c r="C19" s="31"/>
+      <c r="C19" s="24"/>
       <c r="D19" s="21"/>
-      <c r="E19" s="31"/>
+      <c r="E19" s="24"/>
       <c r="F19" s="21"/>
-      <c r="G19" s="31"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="21"/>
-      <c r="I19" s="31"/>
+      <c r="I19" s="24"/>
       <c r="J19" s="21"/>
-      <c r="K19" s="31"/>
+      <c r="K19" s="24"/>
       <c r="L19" s="21"/>
-      <c r="M19" s="31"/>
+      <c r="M19" s="24"/>
       <c r="N19" s="21"/>
-      <c r="O19" s="31"/>
+      <c r="O19" s="24"/>
       <c r="P19" s="21"/>
-      <c r="Q19" s="31"/>
+      <c r="Q19" s="24"/>
       <c r="R19" s="21"/>
-      <c r="S19" s="31"/>
+      <c r="S19" s="24"/>
       <c r="T19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U19" s="31"/>
-    </row>
-    <row r="20" ht="60.41" customHeight="1">
+      <c r="U19" s="24"/>
+    </row>
+    <row r="20" ht="143.26" customHeight="1">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
-      <c r="C20" s="29"/>
+      <c r="C20" s="22"/>
       <c r="D20" s="21"/>
-      <c r="E20" s="29"/>
+      <c r="E20" s="22"/>
       <c r="F20" s="21"/>
-      <c r="G20" s="29"/>
+      <c r="G20" s="22"/>
       <c r="H20" s="21"/>
-      <c r="I20" s="29"/>
+      <c r="I20" s="22"/>
       <c r="J20" s="21"/>
-      <c r="K20" s="29"/>
+      <c r="K20" s="22"/>
       <c r="L20" s="21"/>
-      <c r="M20" s="29"/>
+      <c r="M20" s="22"/>
       <c r="N20" s="21"/>
-      <c r="O20" s="29"/>
+      <c r="O20" s="22"/>
       <c r="P20" s="21"/>
-      <c r="Q20" s="29"/>
+      <c r="Q20" s="22"/>
       <c r="R20" s="21"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="25" t="inlineStr">
+      <c r="S20" s="22"/>
+      <c r="T20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="U20" s="33" t="inlineStr">
+      <c r="U20" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60.41" customHeight="1">
+    <row r="21" ht="143.26" customHeight="1">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
-      <c r="C21" s="30"/>
+      <c r="C21" s="23"/>
       <c r="D21" s="21"/>
-      <c r="E21" s="30"/>
+      <c r="E21" s="23"/>
       <c r="F21" s="21"/>
-      <c r="G21" s="30"/>
+      <c r="G21" s="23"/>
       <c r="H21" s="21"/>
-      <c r="I21" s="30"/>
+      <c r="I21" s="23"/>
       <c r="J21" s="21"/>
-      <c r="K21" s="30"/>
+      <c r="K21" s="23"/>
       <c r="L21" s="21"/>
-      <c r="M21" s="30"/>
+      <c r="M21" s="23"/>
       <c r="N21" s="21"/>
-      <c r="O21" s="30"/>
+      <c r="O21" s="23"/>
       <c r="P21" s="21"/>
-      <c r="Q21" s="30"/>
+      <c r="Q21" s="23"/>
       <c r="R21" s="21"/>
-      <c r="S21" s="30"/>
+      <c r="S21" s="23"/>
       <c r="T21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U21" s="30" t="inlineStr">
+      <c r="U21" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60.41" customHeight="1">
+    <row r="22" ht="143.26" customHeight="1">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
-      <c r="C22" s="31"/>
+      <c r="C22" s="24"/>
       <c r="D22" s="21"/>
-      <c r="E22" s="31"/>
+      <c r="E22" s="24"/>
       <c r="F22" s="21"/>
-      <c r="G22" s="31"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="31"/>
+      <c r="I22" s="24"/>
       <c r="J22" s="21"/>
-      <c r="K22" s="31"/>
+      <c r="K22" s="24"/>
       <c r="L22" s="21"/>
-      <c r="M22" s="31"/>
+      <c r="M22" s="24"/>
       <c r="N22" s="21"/>
-      <c r="O22" s="31"/>
+      <c r="O22" s="24"/>
       <c r="P22" s="21"/>
-      <c r="Q22" s="31"/>
+      <c r="Q22" s="24"/>
       <c r="R22" s="21"/>
-      <c r="S22" s="31"/>
+      <c r="S22" s="24"/>
       <c r="T22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U22" s="31"/>
-    </row>
-    <row r="23" ht="60.41" customHeight="1">
+      <c r="U22" s="24"/>
+    </row>
+    <row r="23" ht="143.26" customHeight="1">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
-      <c r="C23" s="29"/>
+      <c r="C23" s="22"/>
       <c r="D23" s="21"/>
-      <c r="E23" s="29"/>
+      <c r="E23" s="22"/>
       <c r="F23" s="21"/>
-      <c r="G23" s="29"/>
+      <c r="G23" s="22"/>
       <c r="H23" s="21"/>
-      <c r="I23" s="29"/>
+      <c r="I23" s="22"/>
       <c r="J23" s="21"/>
-      <c r="K23" s="29"/>
+      <c r="K23" s="22"/>
       <c r="L23" s="21"/>
-      <c r="M23" s="29"/>
+      <c r="M23" s="22"/>
       <c r="N23" s="21"/>
-      <c r="O23" s="29"/>
+      <c r="O23" s="22"/>
       <c r="P23" s="21"/>
-      <c r="Q23" s="29"/>
+      <c r="Q23" s="22"/>
       <c r="R23" s="21"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="25" t="inlineStr">
+      <c r="S23" s="22"/>
+      <c r="T23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U23" s="33" t="inlineStr">
+      <c r="U23" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60.41" customHeight="1">
+    <row r="24" ht="143.26" customHeight="1">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
-      <c r="C24" s="30"/>
+      <c r="C24" s="23"/>
       <c r="D24" s="21"/>
-      <c r="E24" s="30"/>
+      <c r="E24" s="23"/>
       <c r="F24" s="21"/>
-      <c r="G24" s="30"/>
+      <c r="G24" s="23"/>
       <c r="H24" s="21"/>
-      <c r="I24" s="30"/>
+      <c r="I24" s="23"/>
       <c r="J24" s="21"/>
-      <c r="K24" s="30"/>
+      <c r="K24" s="23"/>
       <c r="L24" s="21"/>
-      <c r="M24" s="30"/>
+      <c r="M24" s="23"/>
       <c r="N24" s="21"/>
-      <c r="O24" s="30"/>
+      <c r="O24" s="23"/>
       <c r="P24" s="21"/>
-      <c r="Q24" s="30"/>
+      <c r="Q24" s="23"/>
       <c r="R24" s="21"/>
-      <c r="S24" s="30"/>
+      <c r="S24" s="23"/>
       <c r="T24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U24" s="34" t="inlineStr">
+      <c r="U24" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">쁘</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60.41" customHeight="1">
+    <row r="25" ht="143.26" customHeight="1">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
-      <c r="C25" s="31"/>
+      <c r="C25" s="24"/>
       <c r="D25" s="21"/>
-      <c r="E25" s="31"/>
+      <c r="E25" s="24"/>
       <c r="F25" s="21"/>
-      <c r="G25" s="31"/>
+      <c r="G25" s="24"/>
       <c r="H25" s="21"/>
-      <c r="I25" s="31"/>
+      <c r="I25" s="24"/>
       <c r="J25" s="21"/>
-      <c r="K25" s="31"/>
+      <c r="K25" s="24"/>
       <c r="L25" s="21"/>
-      <c r="M25" s="31"/>
+      <c r="M25" s="24"/>
       <c r="N25" s="21"/>
-      <c r="O25" s="31"/>
+      <c r="O25" s="24"/>
       <c r="P25" s="21"/>
-      <c r="Q25" s="31"/>
+      <c r="Q25" s="24"/>
       <c r="R25" s="21"/>
-      <c r="S25" s="31"/>
+      <c r="S25" s="24"/>
       <c r="T25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U25" s="31" t="inlineStr">
+      <c r="U25" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60.41" customHeight="1">
+    <row r="26" ht="143.26" customHeight="1">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
-      <c r="C26" s="29"/>
+      <c r="C26" s="22"/>
       <c r="D26" s="21"/>
-      <c r="E26" s="29"/>
+      <c r="E26" s="22"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="29"/>
+      <c r="G26" s="22"/>
       <c r="H26" s="21"/>
-      <c r="I26" s="29"/>
+      <c r="I26" s="22"/>
       <c r="J26" s="21"/>
-      <c r="K26" s="29"/>
+      <c r="K26" s="22"/>
       <c r="L26" s="21"/>
-      <c r="M26" s="29"/>
+      <c r="M26" s="22"/>
       <c r="N26" s="21"/>
-      <c r="O26" s="29"/>
+      <c r="O26" s="22"/>
       <c r="P26" s="21"/>
-      <c r="Q26" s="29"/>
+      <c r="Q26" s="22"/>
       <c r="R26" s="21"/>
-      <c r="S26" s="29"/>
+      <c r="S26" s="22"/>
       <c r="T26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U26" s="29" t="inlineStr">
+      <c r="U26" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60.41" customHeight="1">
+    <row r="27" ht="143.26" customHeight="1">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
-      <c r="C27" s="30"/>
+      <c r="C27" s="23"/>
       <c r="D27" s="21"/>
-      <c r="E27" s="30"/>
+      <c r="E27" s="23"/>
       <c r="F27" s="21"/>
-      <c r="G27" s="30"/>
+      <c r="G27" s="23"/>
       <c r="H27" s="21"/>
-      <c r="I27" s="30"/>
+      <c r="I27" s="23"/>
       <c r="J27" s="21"/>
-      <c r="K27" s="30"/>
+      <c r="K27" s="23"/>
       <c r="L27" s="21"/>
-      <c r="M27" s="30"/>
+      <c r="M27" s="23"/>
       <c r="N27" s="21"/>
-      <c r="O27" s="30"/>
+      <c r="O27" s="23"/>
       <c r="P27" s="21"/>
-      <c r="Q27" s="30"/>
+      <c r="Q27" s="23"/>
       <c r="R27" s="21"/>
-      <c r="S27" s="30"/>
+      <c r="S27" s="23"/>
       <c r="T27" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U27" s="30"/>
-    </row>
-    <row r="28" ht="60.41" customHeight="1">
+      <c r="U27" s="23"/>
+    </row>
+    <row r="28" ht="143.26" customHeight="1">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
-      <c r="C28" s="31"/>
+      <c r="C28" s="24"/>
       <c r="D28" s="21"/>
-      <c r="E28" s="31"/>
+      <c r="E28" s="24"/>
       <c r="F28" s="21"/>
-      <c r="G28" s="31"/>
+      <c r="G28" s="24"/>
       <c r="H28" s="21"/>
-      <c r="I28" s="31"/>
+      <c r="I28" s="24"/>
       <c r="J28" s="21"/>
-      <c r="K28" s="31"/>
+      <c r="K28" s="24"/>
       <c r="L28" s="21"/>
-      <c r="M28" s="31"/>
+      <c r="M28" s="24"/>
       <c r="N28" s="21"/>
-      <c r="O28" s="31"/>
+      <c r="O28" s="24"/>
       <c r="P28" s="21"/>
-      <c r="Q28" s="31"/>
+      <c r="Q28" s="24"/>
       <c r="R28" s="21"/>
-      <c r="S28" s="31"/>
+      <c r="S28" s="24"/>
       <c r="T28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="U28" s="31"/>
+      <c r="U28" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/sheets/민요/검수/새 타령-2.xlsx
+++ b/sheets/민요/검수/새 타령-2.xlsx
@@ -495,10 +495,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/새 타령-2.xlsx
+++ b/sheets/민요/검수/새 타령-2.xlsx
@@ -436,17 +436,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -568,7 +568,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -630,6 +630,54 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4479,993 +4527,993 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:U28"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="17" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="166.67" customHeight="true">
+      <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="18"/>
+      <c r="T2" s="18"/>
+      <c r="U2" s="18"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B3" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="7" t="s">
+      <c r="M3" s="20"/>
+      <c r="N3" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="P3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q3" s="8" t="s">
+      <c r="P3" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="R3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="S3" s="8" t="s">
+      <c r="R3" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="T3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" s="8" t="s">
+      <c r="T3" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" s="20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B4" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="21"/>
+      <c r="F4" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="9" t="s">
+      <c r="G4" s="21"/>
+      <c r="H4" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="7" t="s">
+      <c r="M4" s="21"/>
+      <c r="N4" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="P4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q4" s="9" t="s">
+      <c r="P4" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q4" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="R4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="S4" s="9" t="s">
+      <c r="R4" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="T4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="U4" s="9" t="s">
+      <c r="T4" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="U4" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B5" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="7" t="s">
+      <c r="I5" s="22"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="Q5" s="10" t="s">
+      <c r="Q5" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="R5" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="S5" s="10" t="s">
+      <c r="S5" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="T5" s="7" t="s">
+      <c r="T5" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="U5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="U5" s="22"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B6" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q6" s="8" t="s">
+      <c r="L6" s="19"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="S6" s="8" t="s">
+      <c r="R6" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="S6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="T6" s="7" t="s">
+      <c r="T6" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="U6" s="8" t="s">
+      <c r="U6" s="20" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B7" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="7" t="s">
+      <c r="I7" s="21"/>
+      <c r="J7" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="L7" s="7"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q7" s="9" t="s">
+      <c r="L7" s="19"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q7" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="R7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="S7" s="9" t="s">
+      <c r="R7" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="S7" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="T7" s="7" t="s">
+      <c r="T7" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="U7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="U7" s="21"/>
+    </row>
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B8" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="12" t="s">
+      <c r="G8" s="22"/>
+      <c r="H8" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="7" t="s">
+      <c r="K8" s="22"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="7" t="s">
+      <c r="Q8" s="22"/>
+      <c r="R8" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="S8" s="10"/>
-      <c r="T8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="U8" s="10" t="s">
+      <c r="S8" s="22"/>
+      <c r="T8" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="U8" s="22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B9" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="7" t="s">
+      <c r="L9" s="19"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="R9" s="7" t="s">
+      <c r="R9" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="S9" s="8" t="s">
+      <c r="S9" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="T9" s="7" t="s">
+      <c r="T9" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="U9" s="8" t="s">
+      <c r="U9" s="20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B10" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="21"/>
+      <c r="D10" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="9" t="s">
+      <c r="H10" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="7" t="s">
+      <c r="K10" s="21"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="Q10" s="9" t="s">
+      <c r="Q10" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="R10" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="S10" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="T10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="U10" s="9" t="s">
+      <c r="T10" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="U10" s="21" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B11" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="22"/>
+      <c r="F11" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="7" t="s">
+      <c r="G11" s="22"/>
+      <c r="H11" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="7" t="s">
+      <c r="I11" s="22"/>
+      <c r="J11" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="7" t="s">
+      <c r="L11" s="19"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="Q11" s="10" t="s">
+      <c r="Q11" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="R11" s="7"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="7" t="s">
+      <c r="R11" s="19"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="U11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+      <c r="U11" s="22"/>
+    </row>
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B12" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="8" t="s">
+      <c r="D12" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="7" t="s">
+      <c r="L12" s="19"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="R12" s="7" t="s">
+      <c r="R12" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="S12" s="8" t="s">
+      <c r="S12" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="T12" s="11" t="s">
+      <c r="T12" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="U12" s="14" t="s">
+      <c r="U12" s="26" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B13" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="21"/>
+      <c r="F13" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="9" t="s">
+      <c r="G13" s="21"/>
+      <c r="H13" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K13" s="9" t="s">
+      <c r="J13" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="7" t="s">
+      <c r="L13" s="19"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="Q13" s="9" t="s">
+      <c r="Q13" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="R13" s="7" t="s">
+      <c r="R13" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="S13" s="9" t="s">
+      <c r="S13" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="T13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="U13" s="9" t="s">
+      <c r="T13" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="U13" s="21" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B14" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="22"/>
+      <c r="F14" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="22"/>
+      <c r="J14" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="7" t="s">
+      <c r="M14" s="22"/>
+      <c r="N14" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="7" t="s">
+      <c r="O14" s="22"/>
+      <c r="P14" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="7" t="s">
+      <c r="Q14" s="22"/>
+      <c r="R14" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="6" t="s">
+      <c r="S14" s="22"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="22"/>
+    </row>
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="166.67" customHeight="true">
+      <c r="B16" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-    </row>
-    <row r="17" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="7" t="s">
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="U17" s="8" t="s">
+      <c r="U17" s="20" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="U18" s="9" t="s">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B18" s="19"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="U18" s="21" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="7" t="s">
+    <row r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B19" s="19"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="22"/>
+      <c r="T19" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="U19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="7" t="s">
+      <c r="U19" s="22"/>
+    </row>
+    <row r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="U20" s="8" t="s">
+      <c r="U20" s="20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="9"/>
-      <c r="T21" s="7" t="s">
+    <row r="21" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B21" s="19"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="U21" s="9" t="s">
+      <c r="U21" s="21" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="U22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="7"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="7" t="s">
+    <row r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B22" s="19"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="22"/>
+      <c r="T22" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="U22" s="22"/>
+    </row>
+    <row r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B23" s="19"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="U23" s="8" t="s">
+      <c r="U23" s="20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="7"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="U24" s="15" t="s">
+    <row r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B24" s="19"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="U24" s="27" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="7"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="7" t="s">
+    <row r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B25" s="19"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="22"/>
+      <c r="T25" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="U25" s="10" t="s">
+      <c r="U25" s="22" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="U26" s="8" t="s">
+    <row r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B26" s="19"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="19"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="U26" s="20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="7"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="7" t="s">
+    <row r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B27" s="19"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="U27" s="9"/>
-    </row>
-    <row r="28" customFormat="false" ht="58.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="7"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="10"/>
-      <c r="T28" s="7" t="s">
+      <c r="U27" s="21"/>
+    </row>
+    <row r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+      <c r="B28" s="19"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="22"/>
+      <c r="T28" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="U28" s="10"/>
+      <c r="U28" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5474,7 +5522,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="61" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="24"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/새 타령-2.xlsx
+++ b/sheets/민요/검수/새 타령-2.xlsx
@@ -4556,7 +4556,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="166.67" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
       <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
@@ -4580,7 +4580,7 @@
       <c r="T2" s="18"/>
       <c r="U2" s="18"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B3" s="19" t="s">
         <v>77</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B4" s="19" t="s">
         <v>77</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B5" s="19" t="s">
         <v>77</v>
       </c>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B6" s="19" t="s">
         <v>78</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B7" s="19" t="s">
         <v>107</v>
       </c>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="U7" s="21"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B8" s="19" t="s">
         <v>77</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B9" s="19" t="s">
         <v>82</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B10" s="19" t="s">
         <v>84</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B11" s="19" t="s">
         <v>55</v>
       </c>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B12" s="19" t="s">
         <v>77</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B13" s="19" t="s">
         <v>47</v>
       </c>
@@ -5140,7 +5140,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B14" s="19" t="s">
         <v>58</v>
       </c>
@@ -5187,7 +5187,7 @@
       <c r="U14" s="22"/>
     </row>
     <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="166.67" customHeight="true">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
       <c r="B16" s="18" t="s">
         <v>0</v>
       </c>
@@ -5211,7 +5211,7 @@
       <c r="T16" s="18"/>
       <c r="U16" s="18"/>
     </row>
-    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B17" s="19"/>
       <c r="C17" s="20"/>
       <c r="D17" s="19"/>
@@ -5237,7 +5237,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B18" s="19"/>
       <c r="C18" s="21"/>
       <c r="D18" s="19"/>
@@ -5263,7 +5263,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B19" s="19"/>
       <c r="C19" s="22"/>
       <c r="D19" s="19"/>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B20" s="19"/>
       <c r="C20" s="20"/>
       <c r="D20" s="19"/>
@@ -5313,7 +5313,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="21" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B21" s="19"/>
       <c r="C21" s="21"/>
       <c r="D21" s="19"/>
@@ -5339,7 +5339,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B22" s="19"/>
       <c r="C22" s="22"/>
       <c r="D22" s="19"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="U22" s="22"/>
     </row>
-    <row r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B23" s="19"/>
       <c r="C23" s="20"/>
       <c r="D23" s="19"/>
@@ -5389,7 +5389,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B24" s="19"/>
       <c r="C24" s="21"/>
       <c r="D24" s="19"/>
@@ -5415,7 +5415,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B25" s="19"/>
       <c r="C25" s="22"/>
       <c r="D25" s="19"/>
@@ -5441,7 +5441,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B26" s="19"/>
       <c r="C26" s="20"/>
       <c r="D26" s="19"/>
@@ -5467,7 +5467,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B27" s="19"/>
       <c r="C27" s="21"/>
       <c r="D27" s="19"/>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="U27" s="21"/>
     </row>
-    <row r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="248.92" customHeight="true">
+    <row r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
       <c r="B28" s="19"/>
       <c r="C28" s="22"/>
       <c r="D28" s="19"/>
@@ -5522,7 +5522,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="24"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/새 타령-2.xlsx
+++ b/sheets/민요/검수/새 타령-2.xlsx
@@ -4461,31 +4461,32 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="29.15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="7" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="8" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16383" style="0" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="12.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="86.96" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="80.0" customHeight="true">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
@@ -4509,7 +4510,7 @@
       <c r="T2" s="9"/>
       <c r="U2" s="9"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B3" s="10" t="s">
         <v>65</v>
       </c>
@@ -4571,7 +4572,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B4" s="10" t="s">
         <v>47</v>
       </c>
@@ -4629,7 +4630,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B5" s="10" t="s">
         <v>50</v>
       </c>
@@ -4677,7 +4678,7 @@
       </c>
       <c r="U5" s="13"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B6" s="10" t="s">
         <v>52</v>
       </c>
@@ -4735,7 +4736,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B7" s="10" t="s">
         <v>55</v>
       </c>
@@ -4789,7 +4790,7 @@
       </c>
       <c r="U7" s="12"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B8" s="10" t="s">
         <v>47</v>
       </c>
@@ -4837,7 +4838,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B9" s="10" t="s">
         <v>55</v>
       </c>
@@ -4897,7 +4898,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
@@ -4953,7 +4954,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B11" s="10" t="s">
         <v>58</v>
       </c>
@@ -4999,7 +5000,7 @@
       </c>
       <c r="U11" s="13"/>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B12" s="10" t="s">
         <v>47</v>
       </c>
@@ -5057,7 +5058,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B13" s="10" t="s">
         <v>50</v>
       </c>
@@ -5107,7 +5108,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="129.63" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="119.22" customHeight="true">
       <c r="B14" s="10" t="s">
         <v>70</v>
       </c>
@@ -5160,7 +5161,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
